--- a/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Flore est dans la cuisine. Le chat miaule. Maman dit : on prend soin, avec un adulte. On est doux. Maman prend le bol. Flore reste près de maman. Elles remplissent l'eau avec l'adulte. L'eau est fraîche. Flore pose le bol. Tout doux. Le chat vient. Flore est douce. Elle caresse le dos. Doux, tout doux. Maman dit : avec un adulte, et doux. Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.</t>
+          <t>Flore est dans la cuisine. Le chat miaule. On prend soin, avec un adulte. On est doux. Maman prend le bol. Flore reste près de maman. Elles remplissent l'eau avec l'adulte. L'eau est fraîche. Flore pose le bol. Tout doux. Le chat vient. Flore est douce. Elle caresse le dos. Doux, tout doux. Avec un adulte, et doux. Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Flore est dans la cuisine. Le chat miaule.
+maman|On prend soin, avec un adulte. On est doux. Maman prend le bol.
+narrateur|Flore reste près de maman. Elles remplissent l'eau avec l'adulte. L'eau est fraîche. Flore pose le bol. Tout doux. Le chat vient. Flore est douce. Elle caresse le dos. Doux, tout doux.
+maman|Avec un adulte, et doux.
+narrateur|Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Flore donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Flore a rempli l'eau avec un adulte. Elle a été douce. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Flore s'assoit près de maman. Le chat ronronne.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Flore donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Flore a rempli l'eau avec un adulte. Elle a été douce. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Flore s'assoit près de maman. Le chat ronronne.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Flore donne l'eau au chat</t>
+          <t>L'eau tiède du chat</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut que le chat boive. Elle pense au lait. Le lait est trop froid. Maman verse un peu d'eau tiède. Le chat lape.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Flore est dans la cuisine. Le chat miaule. On prend soin, avec un adulte. On est doux. Maman prend le bol. Flore reste près de maman. Elles remplissent l'eau avec l'adulte. L'eau est fraîche. Flore pose le bol. Tout doux. Le chat vient. Flore est douce. Elle caresse le dos. Doux, tout doux. Avec un adulte, et doux. Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.</t>
+          <t>La bouilloire fait tic, tic, tic. Elle refroidit, tout doux. La cuisine sent le pain grillé. Une miette reste sur la planche. Tu entends, Chouchou ? Tic, tic. Le chat miaule près du buffet. Sa gamelle est vide. Il a soif. Du lait ? Le lait est trop froid. Le chat boit de l'eau. Un peu d'eau tiède. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. En ce moment, Chouchou tient le bol. Le bol est lisse, un peu froid. Tu tiens avec moi ? Oui, maman. Maman verse un peu d'eau. L'eau est tiède. Pas trop. Ça fait un petit chh. C'est chaud ? Tiède, seulement. On pose, tout doux. Chouchou pose la gamelle. Sa main va lentement. Le bol touche le carrelage. Presque pas de bruit. Le chat s'approche. Ses pattes tapent le carrelage. Toc, toc, tout léger. On recule un peu. On reste près de moi. Je reste. Le chat pose la langue. Lape, lape. Il boit. Oui. Une moustache tremble. Une goutte brille. Pas de lait. De l'eau. Pour lui. Le bol sent encore la vapeur. Une petite vapeur, déjà partie.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Flore est dans la cuisine. Le chat miaule. Maman dit : on prend soin, &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. On est doux. Maman prend le bol. Flore reste près de maman. Elles remplissent l'eau avec l'adulte. L'eau est fraîche. Flore pose le bol. Tout doux. Le chat vient. Flore est douce. Elle caresse le dos. Doux, tout doux. Maman dit : avec un adulte, et doux. Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire fait tic, tic, tic. Elle refroidit, tout doux. La cuisine sent le pain grillé. Une miette reste sur la planche. Tu entends, Chouchou ? Tic, tic. Le chat miaule près du buffet. Sa gamelle est vide. Il a soif. Du lait ? Le lait est trop froid. Le chat boit de l'eau. Un peu d'eau tiède. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. En ce moment, Chouchou tient le bol. Le bol est lisse, un peu froid. Tu tiens avec moi ? Oui, maman. Maman verse un peu d'eau. L'eau est tiède. Pas trop. Ça fait un petit chh. C'est chaud ? Tiède, seulement. On pose, tout doux. Chouchou pose la gamelle. Sa main va lentement. Le bol touche le carrelage. Presque pas de bruit. Le chat s'approche. Ses pattes tapent le carrelage. Toc, toc, tout léger. On recule un peu. On reste près de moi. Je reste. Le chat pose la langue. Lape, lape. Il boit. Oui. Une moustache tremble. Une goutte brille. Pas de lait. De l'eau. Pour lui. Le bol sent encore la vapeur. Une petite vapeur, déjà partie.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Flore est dans la cuisine. Le chat miaule.
-maman|On prend soin, avec un adulte. On est doux. Maman prend le bol.
-narrateur|Flore reste près de maman. Elles remplissent l'eau avec l'adulte. L'eau est fraîche. Flore pose le bol. Tout doux. Le chat vient. Flore est douce. Elle caresse le dos. Doux, tout doux.
-maman|Avec un adulte, et doux.
-narrateur|Flore hoche la tête. Le chat lape. Flore sourit. Maman sourit aussi.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La bouilloire fait tic, tic, tic.
+narrateur|Elle refroidit, tout doux.
+narrateur|La cuisine sent le pain grillé.
+narrateur|Une miette reste sur la planche.
+maman|Tu entends, Chouchou ?
+enfant-f|Tic, tic.
+narrateur|Le chat miaule près du buffet.
+narrateur|Sa gamelle est vide.
+enfant-f|Il a soif.
+enfant-f|Du lait ?
+maman|Le lait est trop froid.
+maman|Le chat boit de l'eau.
+maman|Un peu d'eau tiède.
+enfant-f|Je veux qu'il boive.
+maman|On le fait ensemble.
+maman|Avec un adulte.
+maman|On est doux.
+narrateur|En ce moment, Chouchou tient le bol.
+narrateur|Le bol est lisse, un peu froid.
+maman|Tu tiens avec moi ?
+enfant-f|Oui, maman.
+narrateur|Maman verse un peu d'eau.
+narrateur|L'eau est tiède.
+narrateur|Pas trop.
+narrateur|Ça fait un petit chh.
+enfant-f|C'est chaud ?
+maman|Tiède, seulement.
+maman|On pose, tout doux.
+narrateur|Chouchou pose la gamelle.
+narrateur|Sa main va lentement.
+narrateur|Le bol touche le carrelage.
+narrateur|Presque pas de bruit.
+narrateur|Le chat s'approche.
+narrateur|Ses pattes tapent le carrelage.
+narrateur|Toc, toc, tout léger.
+maman|On recule un peu.
+maman|On reste près de moi.
+enfant-f|Je reste.
+narrateur|Le chat pose la langue.
+narrateur|Lape, lape.
+enfant-f|Il boit.
+maman|Oui.
+narrateur|Une moustache tremble.
+narrateur|Une goutte brille.
+enfant-f|Pas de lait.
+maman|De l'eau.
+maman|Pour lui.
+narrateur|Le bol sent encore la vapeur.
+narrateur|Une petite vapeur, déjà partie.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Flore donne l'eau au chat. Comment fait-elle ?</t>
+          <t>Chouchou donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Flore donne l'eau au chat. Comment fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1419,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>doux | avec maman | avec un adulte | tout doux</t>
+          <t>doux | douce | avec maman | avec un adulte | tout doux</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1428,7 +1483,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1555,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Flore donne l'eau au chat. Comment fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou donne l'eau au chat.
+narrateur|Comment fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Flore a rempli l'eau avec un adulte. Elle a été douce. Maman était là.</t>
+          <t>Le chat lape encore. Le bol se vide, tout doux. Il avait soif. Oui. Tu as été douce. Avec un adulte. Merci, Chouchou. Tu as vu l'eau tiède ? Pas froide. Un peu tiède. Chouchou a les mains sur ses genoux. Elle ne prend pas le chat. Le chat se lèche la patte. Il est content. Il a bu. La bouilloire a fini ses tics. Elle est calme. Tic plus. Elle s'est reposée.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Flore a rempli l'eau &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. Elle a été douce. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat lape encore. Le bol se vide, tout doux. Il avait soif. Oui. Tu as été douce. Avec un adulte. Merci, Chouchou. Tu as vu l'eau tiède ? Pas froide. Un peu tiède. Chouchou a les mains sur ses genoux. Elle ne prend pas le chat. Le chat se lèche la patte. Il est content. Il a bu. La bouilloire a fini ses tics. Elle est calme. Tic plus. Elle s'est reposée.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1589,14 +1644,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1727,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Flore a rempli l'eau avec un adulte. Elle a été douce. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le chat lape encore.
+narrateur|Le bol se vide, tout doux.
+enfant-f|Il avait soif.
+maman|Oui.
+maman|Tu as été douce.
+maman|Avec un adulte.
+maman|Merci, Chouchou.
+maman|Tu as vu l'eau tiède ?
+enfant-f|Pas froide.
+maman|Un peu tiède.
+narrateur|Chouchou a les mains sur ses genoux.
+narrateur|Elle ne prend pas le chat.
+narrateur|Le chat se lèche la patte.
+enfant-f|Il est content.
+maman|Il a bu.
+narrateur|La bouilloire a fini ses tics.
+narrateur|Elle est calme.
+enfant-f|Tic plus.
+maman|Elle s'est reposée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Flore s'assoit près de maman. Le chat ronronne.</t>
+          <t>Le chat s'allonge près du buffet. Son poil est chaud, un peu. Un ronron commence. J'entends. Moi aussi. Chouchou s'assoit près de maman. La planche sent encore le pain. On range le bol demain. Il a de l'eau. C'était ça, ton envie. Une miette reste sur le bois. Le chat ferme un œil. Dodo. Un petit dodo, oui. Le carrelage est tiède, comme l'eau. Tu as tenu le bol. Avec toi.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Flore s'assoit près de maman. Le chat ronronne.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat s'allonge près du buffet. Son poil est chaud, un peu. Un ronron commence. J'entends. Moi aussi. Chouchou s'assoit près de maman. La planche sent encore le pain. On range le bol demain. Il a de l'eau. C'était ça, ton envie. Une miette reste sur le bois. Le chat ferme un œil. Dodo. Un petit dodo, oui. Le carrelage est tiède, comme l'eau. Tu as tenu le bol. Avec toi.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1761,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1908,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Flore s'assoit près de maman. Le chat ronronne.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le chat s'allonge près du buffet.
+narrateur|Son poil est chaud, un peu.
+narrateur|Un ronron commence.
+enfant-f|J'entends.
+maman|Moi aussi.
+narrateur|Chouchou s'assoit près de maman.
+narrateur|La planche sent encore le pain.
+maman|On range le bol demain.
+enfant-f|Il a de l'eau.
+maman|C'était ça, ton envie.
+narrateur|Une miette reste sur le bois.
+narrateur|Le chat ferme un œil.
+enfant-f|Dodo.
+maman|Un petit dodo, oui.
+narrateur|Le carrelage est tiède, comme l'eau.
+maman|Tu as tenu le bol.
+enfant-f|Avec toi.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le chat a bu. De l'eau tiède, tout doux. La bouilloire ne fait plus tic. La cuisine sent le pain, encore. Le ronron remplit la pièce.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat a bu. De l'eau tiède, tout doux. La bouilloire ne fait plus tic. La cuisine sent le pain, encore. Le ronron remplit la pièce.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2012,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2091,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le chat a bu.
+maman|De l'eau tiède, tout doux.
+narrateur|La bouilloire ne fait plus tic.
+narrateur|La cuisine sent le pain, encore.
+narrateur|Le ronron remplit la pièce.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, bouilloire, fin d'après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flore, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
